--- a/ds/planejamento/3semestre/planos/Plano_de_Ensino_PPDM1.xlsx
+++ b/ds/planejamento/3semestre/planos/Plano_de_Ensino_PPDM1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESENVOLVIMENTO\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A958F3A-8241-44D4-8B2B-749E54CFB26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0047A411-87A9-4CAC-BF68-D5826C010BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="h9gkGl1sfnRHyr05LFfZmsKJ7cUyj85gDjaHNauDRX4="/>
@@ -565,9 +562,6 @@
     <t>Docente : Wellington Fábio de O. Martins</t>
   </si>
   <si>
-    <t>Data :  21/01/2025</t>
-  </si>
-  <si>
     <t>Data:   /   /2026</t>
   </si>
   <si>
@@ -594,6 +588,9 @@
   <si>
     <t>Desenvolveu o aplicativo que resolve o problema proposto.</t>
   </si>
+  <si>
+    <t>Data :  21/01/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -614,92 +611,109 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0070C0"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="36"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -863,6 +877,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1589,41 +1604,226 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1655,220 +1855,226 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1906,12 +2112,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1921,178 +2121,14 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2108,15 +2144,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2135,18 +2162,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3175,134 +3190,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="58" t="s">
+      <c r="B3" s="141"/>
+      <c r="C3" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="65" t="s">
+      <c r="D3" s="145"/>
+      <c r="E3" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="F3" s="66"/>
-      <c r="G3" s="56" t="s">
+      <c r="F3" s="135"/>
+      <c r="G3" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56" t="s">
+      <c r="H3" s="142"/>
+      <c r="I3" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="56"/>
+      <c r="J3" s="142"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="69" t="s">
+      <c r="A4" s="140"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="138" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="139"/>
+      <c r="G4" s="123" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="70"/>
-      <c r="G4" s="55" t="s">
-        <v>135</v>
-      </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="62" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="86" t="s">
+      <c r="D5" s="119"/>
+      <c r="E5" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="87"/>
-      <c r="G5" s="55" t="s">
+      <c r="F5" s="131"/>
+      <c r="G5" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="79"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="63" t="s">
+      <c r="A6" s="101"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-    </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="78" t="s">
+      <c r="F6" s="133"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+    </row>
+    <row r="7" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="81" t="s">
+      <c r="B7" s="101"/>
+      <c r="C7" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="67" t="s">
+      <c r="D7" s="127"/>
+      <c r="E7" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="79"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
@@ -3323,14 +3338,14 @@
       <c r="F10" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="83" t="s">
+      <c r="G10" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83" t="s">
+      <c r="H10" s="129"/>
+      <c r="I10" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="83"/>
+      <c r="J10" s="129"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -3365,17 +3380,17 @@
       <c r="E11" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="51" t="s">
+      <c r="F11" s="148" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="84" t="s">
+      <c r="G11" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="85"/>
-      <c r="I11" s="84" t="s">
+      <c r="H11" s="56"/>
+      <c r="I11" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="85"/>
+      <c r="J11" s="56"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3410,15 +3425,15 @@
       <c r="E12" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="84" t="s">
+      <c r="F12" s="149"/>
+      <c r="G12" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="85"/>
-      <c r="I12" s="76" t="s">
-        <v>137</v>
+      <c r="H12" s="56"/>
+      <c r="I12" s="124" t="s">
+        <v>136</v>
       </c>
-      <c r="J12" s="77"/>
+      <c r="J12" s="125"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -3453,15 +3468,15 @@
       <c r="E13" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="53"/>
-      <c r="G13" s="84" t="s">
+      <c r="F13" s="150"/>
+      <c r="G13" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="85"/>
-      <c r="I13" s="76" t="s">
-        <v>136</v>
+      <c r="H13" s="56"/>
+      <c r="I13" s="124" t="s">
+        <v>135</v>
       </c>
-      <c r="J13" s="77"/>
+      <c r="J13" s="125"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -3496,17 +3511,17 @@
       <c r="E14" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="54" t="s">
+      <c r="F14" s="151" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="84" t="s">
+      <c r="G14" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="85"/>
-      <c r="I14" s="76" t="s">
-        <v>138</v>
+      <c r="H14" s="56"/>
+      <c r="I14" s="124" t="s">
+        <v>137</v>
       </c>
-      <c r="J14" s="77"/>
+      <c r="J14" s="125"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -3541,15 +3556,15 @@
       <c r="E15" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="52"/>
-      <c r="G15" s="84" t="s">
+      <c r="F15" s="149"/>
+      <c r="G15" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="85"/>
-      <c r="I15" s="76" t="s">
+      <c r="H15" s="56"/>
+      <c r="I15" s="124" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="77"/>
+      <c r="J15" s="125"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -3584,15 +3599,15 @@
       <c r="E16" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="84" t="s">
+      <c r="F16" s="149"/>
+      <c r="G16" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="85"/>
-      <c r="I16" s="244" t="s">
+      <c r="H16" s="56"/>
+      <c r="I16" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="245"/>
+      <c r="J16" s="153"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -3627,13 +3642,13 @@
       <c r="E17" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="84" t="s">
+      <c r="F17" s="149"/>
+      <c r="G17" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="85"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="247"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="154"/>
+      <c r="J17" s="155"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -3668,15 +3683,15 @@
       <c r="E18" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="52"/>
-      <c r="G18" s="84" t="s">
+      <c r="F18" s="149"/>
+      <c r="G18" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="85"/>
-      <c r="I18" s="244" t="s">
+      <c r="H18" s="56"/>
+      <c r="I18" s="152" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="245"/>
+      <c r="J18" s="153"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -3711,13 +3726,13 @@
       <c r="E19" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="53"/>
-      <c r="G19" s="84" t="s">
+      <c r="F19" s="150"/>
+      <c r="G19" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="85"/>
-      <c r="I19" s="246"/>
-      <c r="J19" s="247"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="154"/>
+      <c r="J19" s="155"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -3755,14 +3770,14 @@
       <c r="F20" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="84" t="s">
+      <c r="G20" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="H20" s="85"/>
-      <c r="I20" s="244" t="s">
+      <c r="H20" s="56"/>
+      <c r="I20" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="J20" s="245"/>
+      <c r="J20" s="153"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3800,12 +3815,12 @@
       <c r="F21" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="G21" s="84" t="s">
+      <c r="G21" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="85"/>
-      <c r="I21" s="246"/>
-      <c r="J21" s="247"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="154"/>
+      <c r="J21" s="155"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -3836,10 +3851,10 @@
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="23"/>
-      <c r="G22" s="148"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="151"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3859,18 +3874,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="129" t="s">
+      <c r="A23" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="130"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="130"/>
-      <c r="I23" s="130"/>
-      <c r="J23" s="131"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="74"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3890,18 +3905,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="132" t="s">
+      <c r="A24" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="132"/>
-      <c r="C24" s="132"/>
-      <c r="D24" s="132"/>
-      <c r="E24" s="132"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="132"/>
-      <c r="I24" s="132"/>
-      <c r="J24" s="132"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -3921,18 +3936,18 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="128" t="s">
+      <c r="A25" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="128"/>
-      <c r="I25" s="128"/>
-      <c r="J25" s="128"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -3952,18 +3967,18 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="132" t="s">
+      <c r="A26" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="132"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="132"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -3983,18 +3998,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="128" t="s">
+      <c r="A27" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="128"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="128"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="128"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -4011,18 +4026,18 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A28" s="132" t="s">
+      <c r="A28" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="132"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="132"/>
-      <c r="J28" s="132"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="75"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -4042,18 +4057,18 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="128" t="s">
+      <c r="A29" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="128"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="128"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="128"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -4073,16 +4088,16 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A30" s="136"/>
-      <c r="B30" s="137"/>
-      <c r="C30" s="137"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="137"/>
-      <c r="F30" s="137"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="137"/>
-      <c r="I30" s="137"/>
-      <c r="J30" s="138"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="83"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -4102,16 +4117,16 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="139"/>
-      <c r="B31" s="140"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="140"/>
-      <c r="I31" s="140"/>
-      <c r="J31" s="141"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="86"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -4131,18 +4146,18 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="73" t="s">
+      <c r="A32" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
+      <c r="B32" s="121"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="121"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="121"/>
+      <c r="H32" s="121"/>
+      <c r="I32" s="121"/>
+      <c r="J32" s="121"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -4162,22 +4177,22 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="133" t="s">
+      <c r="A33" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="134"/>
-      <c r="C33" s="134"/>
-      <c r="D33" s="135" t="s">
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="135"/>
-      <c r="F33" s="135"/>
-      <c r="G33" s="74" t="s">
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -4197,12 +4212,12 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="134"/>
-      <c r="B34" s="134"/>
-      <c r="C34" s="134"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
+      <c r="A34" s="79"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
       <c r="G34" s="29">
         <v>1</v>
       </c>
@@ -4234,18 +4249,18 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="121" t="s">
+      <c r="A35" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="88" t="s">
+      <c r="B35" s="108" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="89"/>
-      <c r="D35" s="90" t="s">
+      <c r="C35" s="109"/>
+      <c r="D35" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="E35" s="80"/>
-      <c r="F35" s="79"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="101"/>
       <c r="G35" s="12"/>
       <c r="H35" s="26"/>
       <c r="I35" s="27"/>
@@ -4269,16 +4284,16 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="122"/>
-      <c r="B36" s="88" t="s">
+      <c r="A36" s="106"/>
+      <c r="B36" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="89"/>
-      <c r="D36" s="90" t="s">
+      <c r="C36" s="109"/>
+      <c r="D36" s="110" t="s">
         <v>112</v>
       </c>
-      <c r="E36" s="80"/>
-      <c r="F36" s="79"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="101"/>
       <c r="G36" s="12"/>
       <c r="H36" s="26"/>
       <c r="I36" s="22"/>
@@ -4302,16 +4317,16 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="122"/>
-      <c r="B37" s="97" t="s">
+      <c r="A37" s="106"/>
+      <c r="B37" s="114" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="98"/>
-      <c r="D37" s="101" t="s">
-        <v>142</v>
+      <c r="C37" s="115"/>
+      <c r="D37" s="118" t="s">
+        <v>141</v>
       </c>
-      <c r="E37" s="62"/>
-      <c r="F37" s="102"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="12"/>
       <c r="H37" s="26"/>
       <c r="I37" s="22"/>
@@ -4335,14 +4350,14 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="122"/>
-      <c r="B38" s="99"/>
-      <c r="C38" s="100"/>
-      <c r="D38" s="91" t="s">
-        <v>143</v>
+      <c r="A38" s="106"/>
+      <c r="B38" s="116"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="99" t="s">
+        <v>142</v>
       </c>
-      <c r="E38" s="80"/>
-      <c r="F38" s="79"/>
+      <c r="E38" s="100"/>
+      <c r="F38" s="101"/>
       <c r="G38" s="12"/>
       <c r="H38" s="26"/>
       <c r="I38" s="22"/>
@@ -4366,16 +4381,16 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="122"/>
-      <c r="B39" s="92" t="s">
+      <c r="A39" s="106"/>
+      <c r="B39" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="93"/>
-      <c r="D39" s="94" t="s">
-        <v>141</v>
+      <c r="C39" s="77"/>
+      <c r="D39" s="111" t="s">
+        <v>140</v>
       </c>
-      <c r="E39" s="95"/>
-      <c r="F39" s="96"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="113"/>
       <c r="G39" s="12"/>
       <c r="H39" s="26"/>
       <c r="I39" s="22"/>
@@ -4399,16 +4414,16 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="122"/>
-      <c r="B40" s="92" t="s">
+      <c r="A40" s="106"/>
+      <c r="B40" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="93"/>
-      <c r="D40" s="108" t="s">
+      <c r="C40" s="77"/>
+      <c r="D40" s="94" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="109"/>
-      <c r="F40" s="110"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="96"/>
       <c r="G40" s="12"/>
       <c r="H40" s="26"/>
       <c r="I40" s="22"/>
@@ -4432,16 +4447,16 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="123"/>
-      <c r="B41" s="111" t="s">
+      <c r="A41" s="107"/>
+      <c r="B41" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="112"/>
-      <c r="D41" s="91" t="s">
+      <c r="C41" s="98"/>
+      <c r="D41" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="80"/>
-      <c r="F41" s="79"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="101"/>
       <c r="G41" s="12"/>
       <c r="H41" s="26"/>
       <c r="I41" s="22"/>
@@ -4465,18 +4480,18 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="113" t="s">
+      <c r="A42" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="116" t="s">
+      <c r="B42" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="117"/>
-      <c r="D42" s="118" t="s">
+      <c r="C42" s="71"/>
+      <c r="D42" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="E42" s="119"/>
-      <c r="F42" s="120"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="60"/>
       <c r="G42" s="12"/>
       <c r="H42" s="26"/>
       <c r="I42" s="22"/>
@@ -4500,16 +4515,16 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="114"/>
-      <c r="B43" s="116" t="s">
+      <c r="A43" s="103"/>
+      <c r="B43" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="117"/>
-      <c r="D43" s="118" t="s">
+      <c r="C43" s="71"/>
+      <c r="D43" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="E43" s="119"/>
-      <c r="F43" s="120"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="60"/>
       <c r="G43" s="12"/>
       <c r="H43" s="26"/>
       <c r="I43" s="22"/>
@@ -4533,16 +4548,16 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="114"/>
-      <c r="B44" s="116" t="s">
+      <c r="A44" s="103"/>
+      <c r="B44" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="117"/>
-      <c r="D44" s="118" t="s">
+      <c r="C44" s="71"/>
+      <c r="D44" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="E44" s="119"/>
-      <c r="F44" s="120"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="60"/>
       <c r="G44" s="12"/>
       <c r="H44" s="26"/>
       <c r="I44" s="22"/>
@@ -4566,16 +4581,16 @@
       <c r="AA44" s="1"/>
     </row>
     <row r="45" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="115"/>
-      <c r="B45" s="116" t="s">
+      <c r="A45" s="104"/>
+      <c r="B45" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="117"/>
-      <c r="D45" s="118" t="s">
+      <c r="C45" s="71"/>
+      <c r="D45" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="119"/>
-      <c r="F45" s="120"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="60"/>
       <c r="G45" s="12"/>
       <c r="H45" s="26"/>
       <c r="I45" s="22"/>
@@ -4599,14 +4614,14 @@
       <c r="AA45" s="1"/>
     </row>
     <row r="46" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="107"/>
-      <c r="B46" s="107"/>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
-      <c r="E46" s="107"/>
-      <c r="F46" s="107"/>
-      <c r="G46" s="107"/>
-      <c r="H46" s="107"/>
+      <c r="A46" s="93"/>
+      <c r="B46" s="93"/>
+      <c r="C46" s="93"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="93"/>
+      <c r="H46" s="93"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -4628,18 +4643,18 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="103" t="s">
+      <c r="A47" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="105"/>
-      <c r="F47" s="106" t="s">
+      <c r="B47" s="90"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="91"/>
+      <c r="F47" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="104"/>
-      <c r="H47" s="105"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="91"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -4664,17 +4679,17 @@
       <c r="A48" s="13">
         <v>5</v>
       </c>
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="119"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="120"/>
-      <c r="F48" s="125">
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="61">
         <v>100</v>
       </c>
-      <c r="G48" s="119"/>
-      <c r="H48" s="120"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="60"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -4699,17 +4714,17 @@
       <c r="A49" s="13">
         <v>4</v>
       </c>
-      <c r="B49" s="127" t="s">
+      <c r="B49" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="119"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="120"/>
-      <c r="F49" s="125">
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="61">
         <v>80</v>
       </c>
-      <c r="G49" s="119"/>
-      <c r="H49" s="120"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="60"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -4734,17 +4749,17 @@
       <c r="A50" s="13">
         <v>3</v>
       </c>
-      <c r="B50" s="127" t="s">
+      <c r="B50" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="119"/>
-      <c r="D50" s="119"/>
-      <c r="E50" s="120"/>
-      <c r="F50" s="125">
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="60"/>
+      <c r="F50" s="61">
         <v>65</v>
       </c>
-      <c r="G50" s="119"/>
-      <c r="H50" s="120"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="60"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -4769,17 +4784,17 @@
       <c r="A51" s="13">
         <v>2</v>
       </c>
-      <c r="B51" s="124" t="s">
+      <c r="B51" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="119"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="120"/>
-      <c r="F51" s="125">
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="61">
         <v>50</v>
       </c>
-      <c r="G51" s="119"/>
-      <c r="H51" s="120"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="60"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -4804,17 +4819,17 @@
       <c r="A52" s="13">
         <v>1</v>
       </c>
-      <c r="B52" s="126" t="s">
+      <c r="B52" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="119"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="120"/>
-      <c r="F52" s="125">
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="61">
         <v>30</v>
       </c>
-      <c r="G52" s="119"/>
-      <c r="H52" s="120"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="60"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -4906,16 +4921,16 @@
       <c r="D55" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="143">
+      <c r="E55" s="62">
         <v>1</v>
       </c>
-      <c r="F55" s="143">
+      <c r="F55" s="62">
         <v>0</v>
       </c>
-      <c r="G55" s="75" t="s">
+      <c r="G55" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H55" s="146" t="s">
+      <c r="H55" s="66" t="s">
         <v>26</v>
       </c>
       <c r="I55" s="1"/>
@@ -4945,10 +4960,10 @@
       <c r="D56" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="145"/>
-      <c r="H56" s="147"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="65"/>
+      <c r="H56" s="67"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -4970,18 +4985,18 @@
       <c r="AA56" s="1"/>
     </row>
     <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="142" t="s">
+      <c r="A57" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="142"/>
-      <c r="C57" s="142"/>
-      <c r="D57" s="142"/>
-      <c r="E57" s="142"/>
-      <c r="F57" s="142"/>
-      <c r="G57" s="142"/>
-      <c r="H57" s="142"/>
-      <c r="I57" s="142"/>
-      <c r="J57" s="142"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -5001,16 +5016,16 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="142"/>
-      <c r="B58" s="142"/>
-      <c r="C58" s="142"/>
-      <c r="D58" s="142"/>
-      <c r="E58" s="142"/>
-      <c r="F58" s="142"/>
-      <c r="G58" s="142"/>
-      <c r="H58" s="142"/>
-      <c r="I58" s="142"/>
-      <c r="J58" s="142"/>
+      <c r="A58" s="57"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -31160,41 +31175,51 @@
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A57:J58"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="D33:F34"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="I20:J21"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J8"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="A46:H46"/>
@@ -31211,53 +31236,43 @@
     <mergeCell ref="A35:A41"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="D33:F34"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A29:J29"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J8"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="F14:F19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="I20:J21"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A57:J58"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <hyperlinks>
@@ -31295,16 +31310,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="186" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="204"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="188"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -31325,16 +31340,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="189" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="206"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="207"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="191"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -31355,16 +31370,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="192" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="208"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="192"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -31385,16 +31400,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="209" t="s">
+      <c r="A4" s="193" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="209"/>
-      <c r="C4" s="209"/>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
+      <c r="B4" s="193"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -31415,16 +31430,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="192" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="192"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -31445,14 +31460,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="210"/>
-      <c r="B6" s="210"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="210"/>
+      <c r="A6" s="194"/>
+      <c r="B6" s="194"/>
+      <c r="C6" s="194"/>
+      <c r="D6" s="194"/>
+      <c r="E6" s="194"/>
+      <c r="F6" s="194"/>
+      <c r="G6" s="194"/>
+      <c r="H6" s="194"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -31472,14 +31487,14 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="208"/>
-      <c r="B7" s="208"/>
-      <c r="C7" s="208"/>
-      <c r="D7" s="208"/>
-      <c r="E7" s="208"/>
-      <c r="F7" s="208"/>
-      <c r="G7" s="208"/>
-      <c r="H7" s="208"/>
+      <c r="A7" s="192"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
       <c r="I7" s="7"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -31500,16 +31515,16 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="209" t="s">
+      <c r="A8" s="193" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="211"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="211"/>
-      <c r="E8" s="211"/>
-      <c r="F8" s="211"/>
-      <c r="G8" s="211"/>
-      <c r="H8" s="211"/>
+      <c r="B8" s="195"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="195"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="195"/>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -31530,16 +31545,16 @@
       <c r="Z8" s="10"/>
     </row>
     <row r="9" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="208" t="s">
+      <c r="A9" s="192" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="192"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="192"/>
+      <c r="F9" s="192"/>
+      <c r="G9" s="192"/>
+      <c r="H9" s="192"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -31559,16 +31574,16 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="163" t="s">
+      <c r="A10" s="228" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="163"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="163"/>
-      <c r="F10" s="163"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
+      <c r="B10" s="228"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="228"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="228"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -31589,22 +31604,22 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="220" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="156"/>
-      <c r="C11" s="161"/>
-      <c r="D11" s="155" t="s">
+      <c r="B11" s="221"/>
+      <c r="C11" s="226"/>
+      <c r="D11" s="220" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="152" t="s">
+      <c r="E11" s="221"/>
+      <c r="F11" s="221"/>
+      <c r="G11" s="222"/>
+      <c r="H11" s="217" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="153"/>
-      <c r="J11" s="154"/>
+      <c r="I11" s="218"/>
+      <c r="J11" s="219"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -31623,13 +31638,13 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="158"/>
-      <c r="B12" s="159"/>
-      <c r="C12" s="162"/>
-      <c r="D12" s="158"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="160"/>
+      <c r="A12" s="223"/>
+      <c r="B12" s="224"/>
+      <c r="C12" s="227"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="224"/>
+      <c r="F12" s="224"/>
+      <c r="G12" s="225"/>
       <c r="H12" s="49" t="s">
         <v>13</v>
       </c>
@@ -31657,18 +31672,18 @@
       <c r="Z12" s="8"/>
     </row>
     <row r="13" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="225" t="s">
+      <c r="A13" s="177" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="164" t="s">
+      <c r="B13" s="180" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="165"/>
-      <c r="D13" s="166" t="s">
+      <c r="C13" s="181"/>
+      <c r="D13" s="229" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="167"/>
-      <c r="F13" s="168"/>
+      <c r="E13" s="230"/>
+      <c r="F13" s="231"/>
       <c r="G13" s="50" t="s">
         <v>25</v>
       </c>
@@ -31694,16 +31709,16 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="226"/>
-      <c r="B14" s="88" t="s">
+      <c r="A14" s="178"/>
+      <c r="B14" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="169"/>
-      <c r="D14" s="170" t="s">
+      <c r="C14" s="206"/>
+      <c r="D14" s="207" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="171"/>
-      <c r="F14" s="172"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="209"/>
       <c r="G14" s="50" t="s">
         <v>25</v>
       </c>
@@ -31729,16 +31744,16 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="226"/>
-      <c r="B15" s="173" t="s">
+      <c r="A15" s="178"/>
+      <c r="B15" s="210" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="174"/>
-      <c r="D15" s="108" t="s">
+      <c r="C15" s="211"/>
+      <c r="D15" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="175"/>
-      <c r="F15" s="176"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="157"/>
       <c r="G15" s="50" t="s">
         <v>25</v>
       </c>
@@ -31764,16 +31779,16 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="226"/>
-      <c r="B16" s="177" t="s">
+      <c r="A16" s="178"/>
+      <c r="B16" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="178"/>
-      <c r="D16" s="179" t="s">
+      <c r="C16" s="213"/>
+      <c r="D16" s="214" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="180"/>
-      <c r="F16" s="181"/>
+      <c r="E16" s="215"/>
+      <c r="F16" s="216"/>
       <c r="G16" s="50" t="s">
         <v>25</v>
       </c>
@@ -31799,16 +31814,16 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="226"/>
-      <c r="B17" s="164" t="s">
+      <c r="A17" s="178"/>
+      <c r="B17" s="180" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="165"/>
-      <c r="D17" s="108" t="s">
+      <c r="C17" s="181"/>
+      <c r="D17" s="94" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="175"/>
-      <c r="F17" s="176"/>
+      <c r="E17" s="156"/>
+      <c r="F17" s="157"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -31834,16 +31849,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="227"/>
-      <c r="B18" s="88" t="s">
+      <c r="A18" s="179"/>
+      <c r="B18" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="182"/>
-      <c r="D18" s="183" t="s">
+      <c r="C18" s="199"/>
+      <c r="D18" s="200" t="s">
         <v>114</v>
       </c>
-      <c r="E18" s="175"/>
-      <c r="F18" s="176"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="157"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -31869,18 +31884,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="218" t="s">
+      <c r="A19" s="165" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="220" t="s">
+      <c r="B19" s="167" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="221"/>
-      <c r="D19" s="222" t="s">
+      <c r="C19" s="168"/>
+      <c r="D19" s="169" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="223"/>
-      <c r="F19" s="224"/>
+      <c r="E19" s="170"/>
+      <c r="F19" s="171"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -31906,16 +31921,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="113"/>
-      <c r="B20" s="200" t="s">
+      <c r="A20" s="102"/>
+      <c r="B20" s="172" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="201"/>
-      <c r="D20" s="215" t="s">
+      <c r="C20" s="173"/>
+      <c r="D20" s="174" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="216"/>
-      <c r="F20" s="217"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="176"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -31941,16 +31956,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="113"/>
-      <c r="B21" s="200" t="s">
+      <c r="A21" s="102"/>
+      <c r="B21" s="172" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="201"/>
-      <c r="D21" s="215" t="s">
+      <c r="C21" s="173"/>
+      <c r="D21" s="174" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="216"/>
-      <c r="F21" s="217"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -31976,16 +31991,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="219"/>
-      <c r="B22" s="200" t="s">
+      <c r="A22" s="166"/>
+      <c r="B22" s="172" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="201"/>
-      <c r="D22" s="215" t="s">
+      <c r="C22" s="173"/>
+      <c r="D22" s="174" t="s">
         <v>121</v>
       </c>
-      <c r="E22" s="216"/>
-      <c r="F22" s="217"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="176"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -32039,18 +32054,18 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="103" t="s">
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="158"/>
+      <c r="F24" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="106"/>
-      <c r="H24" s="186"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="158"/>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -32074,17 +32089,17 @@
       <c r="A25" s="13">
         <v>5</v>
       </c>
-      <c r="B25" s="193" t="s">
+      <c r="B25" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="194"/>
-      <c r="D25" s="194"/>
-      <c r="E25" s="195"/>
-      <c r="F25" s="187">
+      <c r="C25" s="160"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="162">
         <v>100</v>
       </c>
-      <c r="G25" s="188"/>
-      <c r="H25" s="189"/>
+      <c r="G25" s="163"/>
+      <c r="H25" s="164"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -32108,17 +32123,17 @@
       <c r="A26" s="13">
         <v>4</v>
       </c>
-      <c r="B26" s="212" t="s">
+      <c r="B26" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="213"/>
-      <c r="D26" s="213"/>
-      <c r="E26" s="214"/>
-      <c r="F26" s="187">
+      <c r="C26" s="197"/>
+      <c r="D26" s="197"/>
+      <c r="E26" s="198"/>
+      <c r="F26" s="162">
         <v>80</v>
       </c>
-      <c r="G26" s="188"/>
-      <c r="H26" s="189"/>
+      <c r="G26" s="163"/>
+      <c r="H26" s="164"/>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -32142,17 +32157,17 @@
       <c r="A27" s="13">
         <v>3</v>
       </c>
-      <c r="B27" s="212" t="s">
+      <c r="B27" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="213"/>
-      <c r="D27" s="213"/>
-      <c r="E27" s="214"/>
-      <c r="F27" s="187">
+      <c r="C27" s="197"/>
+      <c r="D27" s="197"/>
+      <c r="E27" s="198"/>
+      <c r="F27" s="162">
         <v>65</v>
       </c>
-      <c r="G27" s="188"/>
-      <c r="H27" s="189"/>
+      <c r="G27" s="163"/>
+      <c r="H27" s="164"/>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -32176,17 +32191,17 @@
       <c r="A28" s="13">
         <v>2</v>
       </c>
-      <c r="B28" s="190" t="s">
+      <c r="B28" s="203" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="191"/>
-      <c r="D28" s="191"/>
-      <c r="E28" s="192"/>
-      <c r="F28" s="187">
+      <c r="C28" s="204"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="205"/>
+      <c r="F28" s="162">
         <v>50</v>
       </c>
-      <c r="G28" s="188"/>
-      <c r="H28" s="189"/>
+      <c r="G28" s="163"/>
+      <c r="H28" s="164"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -32210,17 +32225,17 @@
       <c r="A29" s="13">
         <v>1</v>
       </c>
-      <c r="B29" s="193" t="s">
+      <c r="B29" s="159" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="194"/>
-      <c r="D29" s="194"/>
-      <c r="E29" s="195"/>
-      <c r="F29" s="187">
+      <c r="C29" s="160"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="162">
         <v>30</v>
       </c>
-      <c r="G29" s="188"/>
-      <c r="H29" s="189"/>
+      <c r="G29" s="163"/>
+      <c r="H29" s="164"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -32309,16 +32324,16 @@
       <c r="D32" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="184">
+      <c r="E32" s="201">
         <v>1</v>
       </c>
-      <c r="F32" s="184">
+      <c r="F32" s="201">
         <v>0</v>
       </c>
-      <c r="G32" s="196" t="s">
+      <c r="G32" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="198" t="s">
+      <c r="H32" s="184" t="s">
         <v>26</v>
       </c>
       <c r="I32" s="7"/>
@@ -32347,10 +32362,10 @@
       <c r="D33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="185"/>
-      <c r="F33" s="185"/>
-      <c r="G33" s="197"/>
-      <c r="H33" s="199"/>
+      <c r="E33" s="202"/>
+      <c r="F33" s="202"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="185"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -38200,19 +38215,25 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="D11:G12"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="H32:H33"/>
     <mergeCell ref="B20:C20"/>
@@ -38229,28 +38250,22 @@
     <mergeCell ref="F26:H26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="D11:G12"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -38277,16 +38292,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="186" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="204"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="188"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -38307,16 +38322,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="189" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="206"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="207"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="191"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -38337,16 +38352,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="192" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="208"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="192"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -38367,16 +38382,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="209" t="s">
+      <c r="A4" s="193" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="209"/>
-      <c r="C4" s="209"/>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
+      <c r="B4" s="193"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -38397,16 +38412,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:27" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="192" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="192"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -38427,14 +38442,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="210"/>
-      <c r="B6" s="210"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="210"/>
+      <c r="A6" s="194"/>
+      <c r="B6" s="194"/>
+      <c r="C6" s="194"/>
+      <c r="D6" s="194"/>
+      <c r="E6" s="194"/>
+      <c r="F6" s="194"/>
+      <c r="G6" s="194"/>
+      <c r="H6" s="194"/>
       <c r="J6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -38453,14 +38468,14 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="208"/>
-      <c r="B7" s="208"/>
-      <c r="C7" s="208"/>
-      <c r="D7" s="208"/>
-      <c r="E7" s="208"/>
-      <c r="F7" s="208"/>
-      <c r="G7" s="208"/>
-      <c r="H7" s="208"/>
+      <c r="A7" s="192"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
       <c r="I7" s="7"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -38481,16 +38496,16 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="209" t="s">
+      <c r="A8" s="193" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="211"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="211"/>
-      <c r="E8" s="211"/>
-      <c r="F8" s="211"/>
-      <c r="G8" s="211"/>
-      <c r="H8" s="211"/>
+      <c r="B8" s="195"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="195"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="195"/>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -38511,16 +38526,16 @@
       <c r="Z8" s="10"/>
     </row>
     <row r="9" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="208" t="s">
+      <c r="A9" s="192" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="192"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="192"/>
+      <c r="F9" s="192"/>
+      <c r="G9" s="192"/>
+      <c r="H9" s="192"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -38540,16 +38555,16 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="228" t="s">
+      <c r="A10" s="235" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="229"/>
-      <c r="C10" s="229"/>
-      <c r="D10" s="229"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="229"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="230"/>
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="236"/>
+      <c r="E10" s="236"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="237"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -38570,22 +38585,22 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="220" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="231"/>
-      <c r="C11" s="232"/>
-      <c r="D11" s="156" t="s">
+      <c r="B11" s="238"/>
+      <c r="C11" s="239"/>
+      <c r="D11" s="221" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="231"/>
-      <c r="F11" s="231"/>
-      <c r="G11" s="231"/>
-      <c r="H11" s="234" t="s">
+      <c r="E11" s="238"/>
+      <c r="F11" s="238"/>
+      <c r="G11" s="238"/>
+      <c r="H11" s="241" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="234"/>
-      <c r="J11" s="234"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -38604,13 +38619,13 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="233"/>
-      <c r="B12" s="119"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
+      <c r="A12" s="240"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="49" t="s">
         <v>13</v>
       </c>
@@ -38638,18 +38653,18 @@
       <c r="Z12" s="8"/>
     </row>
     <row r="13" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="121" t="s">
+      <c r="A13" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="108" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="89"/>
-      <c r="D13" s="90" t="s">
+      <c r="C13" s="109"/>
+      <c r="D13" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="79"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="101"/>
       <c r="G13" s="50" t="s">
         <v>25</v>
       </c>
@@ -38675,16 +38690,16 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="122"/>
-      <c r="B14" s="88" t="s">
+      <c r="A14" s="106"/>
+      <c r="B14" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="89"/>
-      <c r="D14" s="90" t="s">
+      <c r="C14" s="109"/>
+      <c r="D14" s="110" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="80"/>
-      <c r="F14" s="79"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="101"/>
       <c r="G14" s="50" t="s">
         <v>25</v>
       </c>
@@ -38710,16 +38725,16 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="122"/>
-      <c r="B15" s="235" t="s">
+      <c r="A15" s="106"/>
+      <c r="B15" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="236"/>
-      <c r="D15" s="91" t="s">
+      <c r="C15" s="234"/>
+      <c r="D15" s="99" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="80"/>
-      <c r="F15" s="79"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="50" t="s">
         <v>25</v>
       </c>
@@ -38745,16 +38760,16 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="122"/>
-      <c r="B16" s="92" t="s">
+      <c r="A16" s="106"/>
+      <c r="B16" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="93"/>
-      <c r="D16" s="94" t="s">
+      <c r="C16" s="77"/>
+      <c r="D16" s="111" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="95"/>
-      <c r="F16" s="96"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="113"/>
       <c r="G16" s="50" t="s">
         <v>25</v>
       </c>
@@ -38780,16 +38795,16 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="122"/>
-      <c r="B17" s="92" t="s">
+      <c r="A17" s="106"/>
+      <c r="B17" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="93"/>
-      <c r="D17" s="108" t="s">
+      <c r="C17" s="77"/>
+      <c r="D17" s="94" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="109"/>
-      <c r="F17" s="110"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="96"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -38815,16 +38830,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="123"/>
-      <c r="B18" s="111" t="s">
+      <c r="A18" s="107"/>
+      <c r="B18" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="112"/>
-      <c r="D18" s="91" t="s">
+      <c r="C18" s="98"/>
+      <c r="D18" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="E18" s="80"/>
-      <c r="F18" s="79"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="101"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -38850,18 +38865,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="116" t="s">
+      <c r="B19" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="117"/>
-      <c r="D19" s="118" t="s">
+      <c r="C19" s="71"/>
+      <c r="D19" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="60"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -38887,16 +38902,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="114"/>
-      <c r="B20" s="116" t="s">
+      <c r="A20" s="103"/>
+      <c r="B20" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118" t="s">
+      <c r="C20" s="71"/>
+      <c r="D20" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="119"/>
-      <c r="F20" s="120"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="60"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -38922,16 +38937,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="114"/>
-      <c r="B21" s="116" t="s">
+      <c r="A21" s="103"/>
+      <c r="B21" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118" t="s">
+      <c r="C21" s="71"/>
+      <c r="D21" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="60"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -38957,16 +38972,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="115"/>
-      <c r="B22" s="116" t="s">
+      <c r="A22" s="104"/>
+      <c r="B22" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118" t="s">
+      <c r="C22" s="71"/>
+      <c r="D22" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="60"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -39020,18 +39035,18 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="104"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="105"/>
-      <c r="F24" s="106" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="105"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="91"/>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
@@ -39055,17 +39070,17 @@
       <c r="A25" s="13">
         <v>5</v>
       </c>
-      <c r="B25" s="126" t="s">
+      <c r="B25" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="125">
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="61">
         <v>100</v>
       </c>
-      <c r="G25" s="119"/>
-      <c r="H25" s="120"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -39089,17 +39104,17 @@
       <c r="A26" s="13">
         <v>4</v>
       </c>
-      <c r="B26" s="127" t="s">
+      <c r="B26" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="125">
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="61">
         <v>80</v>
       </c>
-      <c r="G26" s="119"/>
-      <c r="H26" s="120"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="60"/>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -39123,17 +39138,17 @@
       <c r="A27" s="13">
         <v>3</v>
       </c>
-      <c r="B27" s="127" t="s">
+      <c r="B27" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="125">
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="61">
         <v>65</v>
       </c>
-      <c r="G27" s="119"/>
-      <c r="H27" s="120"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -39157,17 +39172,17 @@
       <c r="A28" s="13">
         <v>2</v>
       </c>
-      <c r="B28" s="124" t="s">
+      <c r="B28" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="125">
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="61">
         <v>50</v>
       </c>
-      <c r="G28" s="119"/>
-      <c r="H28" s="120"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="60"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -39191,17 +39206,17 @@
       <c r="A29" s="13">
         <v>1</v>
       </c>
-      <c r="B29" s="126" t="s">
+      <c r="B29" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="125">
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="61">
         <v>30</v>
       </c>
-      <c r="G29" s="119"/>
-      <c r="H29" s="120"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="60"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -39290,16 +39305,16 @@
       <c r="D32" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="237">
+      <c r="E32" s="232">
         <v>1</v>
       </c>
-      <c r="F32" s="237">
+      <c r="F32" s="232">
         <v>0</v>
       </c>
-      <c r="G32" s="196" t="s">
+      <c r="G32" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="198" t="s">
+      <c r="H32" s="184" t="s">
         <v>26</v>
       </c>
       <c r="I32" s="7"/>
@@ -39328,10 +39343,10 @@
       <c r="D33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="120"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="197"/>
-      <c r="H33" s="199"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="185"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -45181,23 +45196,24 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D11:G12"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="A19:A22"/>
@@ -45214,24 +45230,23 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D11:G12"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -45258,16 +45273,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="186" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="204"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="188"/>
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -45288,16 +45303,16 @@
       <c r="Z1" s="8"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="189" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="206"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="207"/>
+      <c r="B2" s="190"/>
+      <c r="C2" s="190"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="191"/>
       <c r="I2" s="7"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
@@ -45318,16 +45333,16 @@
       <c r="Z2" s="8"/>
     </row>
     <row r="3" spans="1:26" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="192" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="208"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="192"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -45348,16 +45363,16 @@
       <c r="Z3" s="8"/>
     </row>
     <row r="4" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="209" t="s">
+      <c r="A4" s="193" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="209"/>
-      <c r="C4" s="209"/>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
+      <c r="B4" s="193"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
       <c r="I4" s="7"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -45378,16 +45393,16 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5" spans="1:26" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="192" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="192"/>
       <c r="I5" s="7"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
@@ -45408,14 +45423,14 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="210"/>
-      <c r="B6" s="210"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="210"/>
+      <c r="A6" s="194"/>
+      <c r="B6" s="194"/>
+      <c r="C6" s="194"/>
+      <c r="D6" s="194"/>
+      <c r="E6" s="194"/>
+      <c r="F6" s="194"/>
+      <c r="G6" s="194"/>
+      <c r="H6" s="194"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -45435,16 +45450,16 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7" spans="1:26" ht="192" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="208" t="s">
+      <c r="A7" s="192" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="208"/>
-      <c r="C7" s="208"/>
-      <c r="D7" s="208"/>
-      <c r="E7" s="208"/>
-      <c r="F7" s="208"/>
-      <c r="G7" s="208"/>
-      <c r="H7" s="208"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -45464,14 +45479,14 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="208"/>
-      <c r="B8" s="208"/>
-      <c r="C8" s="208"/>
-      <c r="D8" s="208"/>
-      <c r="E8" s="208"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="208"/>
-      <c r="H8" s="208"/>
+      <c r="A8" s="192"/>
+      <c r="B8" s="192"/>
+      <c r="C8" s="192"/>
+      <c r="D8" s="192"/>
+      <c r="E8" s="192"/>
+      <c r="F8" s="192"/>
+      <c r="G8" s="192"/>
+      <c r="H8" s="192"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -45491,16 +45506,16 @@
       <c r="Z8" s="8"/>
     </row>
     <row r="9" spans="1:26" ht="365.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="208" t="s">
+      <c r="A9" s="192" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="192"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="192"/>
+      <c r="F9" s="192"/>
+      <c r="G9" s="192"/>
+      <c r="H9" s="192"/>
       <c r="I9" s="7"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
@@ -45521,14 +45536,14 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10" spans="1:26" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="238"/>
-      <c r="B10" s="239"/>
-      <c r="C10" s="239"/>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="240"/>
+      <c r="A10" s="242"/>
+      <c r="B10" s="243"/>
+      <c r="C10" s="243"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="244"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -45548,16 +45563,16 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11" spans="1:26" ht="240.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="241" t="s">
+      <c r="A11" s="245" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="242"/>
-      <c r="C11" s="242"/>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="243"/>
+      <c r="B11" s="246"/>
+      <c r="C11" s="246"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="247"/>
       <c r="I11" s="7"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -45578,16 +45593,16 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="209" t="s">
+      <c r="A12" s="193" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="211"/>
-      <c r="C12" s="211"/>
-      <c r="D12" s="211"/>
-      <c r="E12" s="211"/>
-      <c r="F12" s="211"/>
-      <c r="G12" s="211"/>
-      <c r="H12" s="211"/>
+      <c r="B12" s="195"/>
+      <c r="C12" s="195"/>
+      <c r="D12" s="195"/>
+      <c r="E12" s="195"/>
+      <c r="F12" s="195"/>
+      <c r="G12" s="195"/>
+      <c r="H12" s="195"/>
       <c r="I12" s="9"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -45608,16 +45623,16 @@
       <c r="Z12" s="10"/>
     </row>
     <row r="13" spans="1:26" ht="246" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="208" t="s">
+      <c r="A13" s="192" t="s">
         <v>132</v>
       </c>
-      <c r="B13" s="208"/>
-      <c r="C13" s="208"/>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="208"/>
-      <c r="G13" s="208"/>
-      <c r="H13" s="208"/>
+      <c r="B13" s="192"/>
+      <c r="C13" s="192"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="192"/>
+      <c r="H13" s="192"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -45637,16 +45652,16 @@
       <c r="Z13" s="8"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="228" t="s">
+      <c r="A14" s="235" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="229"/>
-      <c r="C14" s="229"/>
-      <c r="D14" s="229"/>
-      <c r="E14" s="229"/>
-      <c r="F14" s="229"/>
-      <c r="G14" s="229"/>
-      <c r="H14" s="230"/>
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="236"/>
+      <c r="E14" s="236"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="236"/>
+      <c r="H14" s="237"/>
       <c r="I14" s="7"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -45667,22 +45682,22 @@
       <c r="Z14" s="8"/>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="220" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="231"/>
-      <c r="C15" s="232"/>
-      <c r="D15" s="156" t="s">
+      <c r="B15" s="238"/>
+      <c r="C15" s="239"/>
+      <c r="D15" s="221" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="231"/>
-      <c r="F15" s="231"/>
-      <c r="G15" s="231"/>
-      <c r="H15" s="234" t="s">
+      <c r="E15" s="238"/>
+      <c r="F15" s="238"/>
+      <c r="G15" s="238"/>
+      <c r="H15" s="241" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="234"/>
-      <c r="J15" s="234"/>
+      <c r="I15" s="241"/>
+      <c r="J15" s="241"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
@@ -45701,13 +45716,13 @@
       <c r="Z15" s="8"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="233"/>
-      <c r="B16" s="119"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
+      <c r="A16" s="240"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
       <c r="H16" s="49" t="s">
         <v>13</v>
       </c>
@@ -45735,18 +45750,18 @@
       <c r="Z16" s="8"/>
     </row>
     <row r="17" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="108" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="89"/>
-      <c r="D17" s="90" t="s">
+      <c r="C17" s="109"/>
+      <c r="D17" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="80"/>
-      <c r="F17" s="79"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="101"/>
       <c r="G17" s="50" t="s">
         <v>25</v>
       </c>
@@ -45772,16 +45787,16 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="122"/>
-      <c r="B18" s="88" t="s">
+      <c r="A18" s="106"/>
+      <c r="B18" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="89"/>
-      <c r="D18" s="90" t="s">
+      <c r="C18" s="109"/>
+      <c r="D18" s="110" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="80"/>
-      <c r="F18" s="79"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="101"/>
       <c r="G18" s="50" t="s">
         <v>25</v>
       </c>
@@ -45807,16 +45822,16 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="122"/>
-      <c r="B19" s="235" t="s">
+      <c r="A19" s="106"/>
+      <c r="B19" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="236"/>
-      <c r="D19" s="91" t="s">
+      <c r="C19" s="234"/>
+      <c r="D19" s="99" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="80"/>
-      <c r="F19" s="79"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="50" t="s">
         <v>25</v>
       </c>
@@ -45842,16 +45857,16 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="122"/>
-      <c r="B20" s="92" t="s">
+      <c r="A20" s="106"/>
+      <c r="B20" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="93"/>
-      <c r="D20" s="94" t="s">
-        <v>140</v>
+      <c r="C20" s="77"/>
+      <c r="D20" s="111" t="s">
+        <v>139</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="96"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="113"/>
       <c r="G20" s="50" t="s">
         <v>25</v>
       </c>
@@ -45877,16 +45892,16 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="122"/>
-      <c r="B21" s="92" t="s">
+      <c r="A21" s="106"/>
+      <c r="B21" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="93"/>
-      <c r="D21" s="108" t="s">
+      <c r="C21" s="77"/>
+      <c r="D21" s="94" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="109"/>
-      <c r="F21" s="110"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="96"/>
       <c r="G21" s="50" t="s">
         <v>25</v>
       </c>
@@ -45912,16 +45927,16 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="123"/>
-      <c r="B22" s="111" t="s">
+      <c r="A22" s="107"/>
+      <c r="B22" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="112"/>
-      <c r="D22" s="91" t="s">
+      <c r="C22" s="98"/>
+      <c r="D22" s="99" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="80"/>
-      <c r="F22" s="79"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="101"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -45947,18 +45962,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="116" t="s">
+      <c r="B23" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118" t="s">
+      <c r="C23" s="71"/>
+      <c r="D23" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
       <c r="G23" s="50" t="s">
         <v>25</v>
       </c>
@@ -45984,16 +45999,16 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="114"/>
-      <c r="B24" s="116" t="s">
+      <c r="A24" s="103"/>
+      <c r="B24" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118" t="s">
+      <c r="C24" s="71"/>
+      <c r="D24" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="60"/>
       <c r="G24" s="50" t="s">
         <v>25</v>
       </c>
@@ -46019,16 +46034,16 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="114"/>
-      <c r="B25" s="116" t="s">
+      <c r="A25" s="103"/>
+      <c r="B25" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="117"/>
-      <c r="D25" s="118" t="s">
+      <c r="C25" s="71"/>
+      <c r="D25" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="60"/>
       <c r="G25" s="50" t="s">
         <v>25</v>
       </c>
@@ -46054,16 +46069,16 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="115"/>
-      <c r="B26" s="116" t="s">
+      <c r="A26" s="104"/>
+      <c r="B26" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118" t="s">
+      <c r="C26" s="71"/>
+      <c r="D26" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="60"/>
       <c r="G26" s="50" t="s">
         <v>25</v>
       </c>
@@ -46117,18 +46132,18 @@
       <c r="Z27" s="8"/>
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="104"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="106" t="s">
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="104"/>
-      <c r="H28" s="105"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="91"/>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
@@ -46152,17 +46167,17 @@
       <c r="A29" s="13">
         <v>5</v>
       </c>
-      <c r="B29" s="126" t="s">
+      <c r="B29" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="125">
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="61">
         <v>100</v>
       </c>
-      <c r="G29" s="119"/>
-      <c r="H29" s="120"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="60"/>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -46186,17 +46201,17 @@
       <c r="A30" s="13">
         <v>5</v>
       </c>
-      <c r="B30" s="127" t="s">
-        <v>139</v>
+      <c r="B30" s="88" t="s">
+        <v>138</v>
       </c>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="125">
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="61">
         <v>80</v>
       </c>
-      <c r="G30" s="119"/>
-      <c r="H30" s="120"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="60"/>
       <c r="I30" s="7"/>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
@@ -46220,17 +46235,17 @@
       <c r="A31" s="13">
         <v>4</v>
       </c>
-      <c r="B31" s="127" t="s">
+      <c r="B31" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="120"/>
-      <c r="F31" s="125">
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="61">
         <v>70</v>
       </c>
-      <c r="G31" s="119"/>
-      <c r="H31" s="120"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="7"/>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
@@ -46254,17 +46269,17 @@
       <c r="A32" s="13">
         <v>3</v>
       </c>
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="120"/>
-      <c r="F32" s="125">
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="61">
         <v>65</v>
       </c>
-      <c r="G32" s="119"/>
-      <c r="H32" s="120"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="60"/>
       <c r="I32" s="7"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
@@ -46288,17 +46303,17 @@
       <c r="A33" s="13">
         <v>2</v>
       </c>
-      <c r="B33" s="124" t="s">
+      <c r="B33" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="120"/>
-      <c r="F33" s="125">
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="61">
         <v>50</v>
       </c>
-      <c r="G33" s="119"/>
-      <c r="H33" s="120"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="60"/>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -46322,17 +46337,17 @@
       <c r="A34" s="13">
         <v>1</v>
       </c>
-      <c r="B34" s="126" t="s">
+      <c r="B34" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="119"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="120"/>
-      <c r="F34" s="125">
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="61">
         <v>30</v>
       </c>
-      <c r="G34" s="119"/>
-      <c r="H34" s="120"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="60"/>
       <c r="I34" s="7"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
@@ -46421,16 +46436,16 @@
       <c r="D37" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="237">
+      <c r="E37" s="232">
         <v>1</v>
       </c>
-      <c r="F37" s="237">
+      <c r="F37" s="232">
         <v>0</v>
       </c>
-      <c r="G37" s="196" t="s">
+      <c r="G37" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="198" t="s">
+      <c r="H37" s="184" t="s">
         <v>26</v>
       </c>
       <c r="I37" s="7"/>
@@ -46459,10 +46474,10 @@
       <c r="D38" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="120"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="197"/>
-      <c r="H38" s="199"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="183"/>
+      <c r="H38" s="185"/>
       <c r="I38" s="7"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
@@ -52312,6 +52327,47 @@
     <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:C16"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A10:H10"/>
@@ -52328,47 +52384,6 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="A23:A26"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:C16"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="A17:A22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
